--- a/data/trans_dic/P16A03-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A03-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,15</t>
+          <t>1,09; 3,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,7</t>
+          <t>0,37; 1,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,59</t>
+          <t>0,28; 1,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,35</t>
+          <t>1,69; 4,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 8,04</t>
+          <t>4,35; 7,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 7,41</t>
+          <t>3,89; 7,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,65; 6,96</t>
+          <t>3,54; 7,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,45</t>
+          <t>3,49; 5,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 5,06</t>
+          <t>3,01; 5,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,14</t>
+          <t>2,21; 4,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,85</t>
+          <t>2,12; 3,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 4,52</t>
+          <t>2,89; 4,49</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,03</t>
+          <t>1,44; 3,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,03</t>
+          <t>0,64; 2,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,97</t>
+          <t>0,63; 2,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,14</t>
+          <t>0,6; 2,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,99; 7,04</t>
+          <t>4,19; 7,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,12; 8,27</t>
+          <t>5,09; 8,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,29</t>
+          <t>2,08; 4,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,55; 5,79</t>
+          <t>3,62; 5,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 5,04</t>
+          <t>3,15; 4,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 4,81</t>
+          <t>3,01; 4,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,88</t>
+          <t>1,61; 2,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,47</t>
+          <t>1,83; 3,46</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,07</t>
+          <t>0,82; 3,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,23</t>
+          <t>0,73; 3,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,69</t>
+          <t>0,79; 2,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,61</t>
+          <t>1,41; 3,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,24</t>
+          <t>3,75; 7,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,4; 8,11</t>
+          <t>4,44; 8,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,42</t>
+          <t>2,68; 5,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,95</t>
+          <t>1,64; 4,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 4,77</t>
+          <t>2,58; 4,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,1</t>
+          <t>2,98; 5,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,58</t>
+          <t>1,94; 3,7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,89</t>
+          <t>1,86; 3,79</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,76</t>
+          <t>1,76; 3,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,61</t>
+          <t>0,99; 2,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,55</t>
+          <t>0,93; 2,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,19</t>
+          <t>1,36; 3,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,06</t>
+          <t>3,5; 6,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 7,57</t>
+          <t>4,42; 7,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,44</t>
+          <t>3,58; 6,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,36; 8,56</t>
+          <t>5,33; 8,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 4,59</t>
+          <t>2,97; 4,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,87</t>
+          <t>2,98; 4,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,17</t>
+          <t>2,52; 4,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 5,7</t>
+          <t>3,79; 5,63</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,9</t>
+          <t>1,75; 2,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,8</t>
+          <t>0,96; 1,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,72</t>
+          <t>0,97; 1,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,49</t>
+          <t>1,49; 2,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,56; 6,06</t>
+          <t>4,58; 6,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,87</t>
+          <t>5,23; 6,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,88</t>
+          <t>3,46; 4,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 5,65</t>
+          <t>4,08; 5,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,31; 4,24</t>
+          <t>3,35; 4,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,26; 4,2</t>
+          <t>3,29; 4,22</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,16</t>
+          <t>2,4; 3,14</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,0</t>
+          <t>3,02; 3,97</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7715; 21831</t>
+          <t>7577; 22337</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2687; 11928</t>
+          <t>2612; 12590</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1665; 10748</t>
+          <t>1918; 11172</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11782; 27628</t>
+          <t>10707; 26786</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30020; 55370</t>
+          <t>29964; 54949</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25727; 51277</t>
+          <t>26921; 50674</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24536; 46813</t>
+          <t>23852; 47781</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22901; 36812</t>
+          <t>23541; 38406</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>40882; 69923</t>
+          <t>41591; 69859</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31525; 57743</t>
+          <t>30842; 57865</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28155; 51940</t>
+          <t>28514; 53090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38113; 59248</t>
+          <t>37925; 58821</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15455; 38777</t>
+          <t>13836; 36118</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6193; 20709</t>
+          <t>6545; 20585</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6739; 20158</t>
+          <t>6485; 21527</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6937; 25521</t>
+          <t>7166; 26015</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38603; 68176</t>
+          <t>40568; 70534</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52634; 85004</t>
+          <t>52301; 86672</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22185; 44743</t>
+          <t>21710; 47018</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34052; 55500</t>
+          <t>34684; 54436</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>60590; 97278</t>
+          <t>60798; 96052</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61251; 98355</t>
+          <t>61610; 97796</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31803; 59381</t>
+          <t>33231; 60467</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38626; 74683</t>
+          <t>39377; 74499</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4814; 20860</t>
+          <t>5584; 21907</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5168; 24429</t>
+          <t>5541; 25060</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5935; 20411</t>
+          <t>6030; 21474</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9691; 25406</t>
+          <t>9895; 24949</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26501; 49511</t>
+          <t>25649; 49470</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34144; 62944</t>
+          <t>34457; 63796</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20424; 42530</t>
+          <t>21076; 42816</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16155; 46163</t>
+          <t>15293; 45331</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35811; 64925</t>
+          <t>35147; 63580</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45013; 78173</t>
+          <t>45708; 78611</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30072; 55251</t>
+          <t>30040; 57082</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31819; 63733</t>
+          <t>30393; 62009</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16995; 35383</t>
+          <t>16537; 34691</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8823; 24630</t>
+          <t>9381; 26357</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8631; 23913</t>
+          <t>8677; 23696</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12116; 29607</t>
+          <t>12604; 30584</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35777; 62900</t>
+          <t>36343; 64475</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>47688; 79343</t>
+          <t>46323; 80942</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36197; 67175</t>
+          <t>37360; 66157</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>58548; 93422</t>
+          <t>58161; 91309</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>58061; 90903</t>
+          <t>58736; 91221</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58620; 97025</t>
+          <t>59326; 96116</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50813; 82690</t>
+          <t>49980; 84128</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>78293; 115131</t>
+          <t>76585; 113630</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>58615; 94985</t>
+          <t>57390; 91669</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34073; 61591</t>
+          <t>32689; 62370</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31640; 58547</t>
+          <t>32914; 58279</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50926; 86019</t>
+          <t>51668; 87804</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>154147; 204663</t>
+          <t>154672; 206254</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>185300; 243332</t>
+          <t>185266; 243139</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>123591; 172901</t>
+          <t>122626; 175335</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>148904; 206724</t>
+          <t>149245; 208661</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>220429; 281987</t>
+          <t>222735; 286084</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>227342; 292577</t>
+          <t>228931; 294050</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162858; 218963</t>
+          <t>166431; 217995</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>212144; 284391</t>
+          <t>215097; 282375</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A03-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A03-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,22</t>
+          <t>1,0; 3,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,8</t>
+          <t>0,29; 1,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,66</t>
+          <t>0,28; 1,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,22</t>
+          <t>1,75; 4,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 7,98</t>
+          <t>4,32; 7,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 7,32</t>
+          <t>3,81; 7,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,1</t>
+          <t>3,46; 7,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 5,69</t>
+          <t>3,37; 5,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,06</t>
+          <t>2,97; 5,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,15</t>
+          <t>2,33; 4,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,94</t>
+          <t>2,16; 4,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,49</t>
+          <t>2,86; 4,49</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,76</t>
+          <t>1,53; 3,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,02</t>
+          <t>0,59; 1,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,11</t>
+          <t>0,58; 1,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,18</t>
+          <t>1,04; 2,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,28</t>
+          <t>4,03; 7,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,09; 8,43</t>
+          <t>5,06; 8,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,51</t>
+          <t>2,14; 4,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,62; 5,68</t>
+          <t>3,58; 5,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,98</t>
+          <t>3,1; 5,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 4,78</t>
+          <t>2,99; 4,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,93</t>
+          <t>1,53; 2,89</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,46</t>
+          <t>2,49; 3,74</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,23</t>
+          <t>0,78; 3,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,31</t>
+          <t>0,72; 3,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,83</t>
+          <t>0,77; 2,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,55</t>
+          <t>1,54; 4,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,23</t>
+          <t>3,93; 7,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 8,22</t>
+          <t>4,36; 8,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 5,45</t>
+          <t>2,77; 5,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,86</t>
+          <t>3,68; 6,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,67</t>
+          <t>2,56; 4,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 5,13</t>
+          <t>2,94; 5,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,7</t>
+          <t>1,97; 3,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,79</t>
+          <t>2,95; 4,82</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,68</t>
+          <t>1,85; 3,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,79</t>
+          <t>0,94; 2,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,53</t>
+          <t>0,94; 2,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,3</t>
+          <t>1,33; 3,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,21</t>
+          <t>3,56; 6,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 7,73</t>
+          <t>4,42; 7,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,34</t>
+          <t>3,51; 6,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 8,37</t>
+          <t>5,95; 8,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 4,61</t>
+          <t>2,96; 4,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,83</t>
+          <t>3,1; 4,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,25</t>
+          <t>2,47; 4,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,63</t>
+          <t>4,03; 5,74</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,8</t>
+          <t>1,74; 2,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,82</t>
+          <t>0,93; 1,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,72</t>
+          <t>0,94; 1,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,54</t>
+          <t>1,7; 2,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 6,1</t>
+          <t>4,52; 6,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,86</t>
+          <t>5,22; 6,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,46; 4,95</t>
+          <t>3,48; 4,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,08; 5,7</t>
+          <t>4,78; 6,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,35; 4,3</t>
+          <t>3,37; 4,37</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 4,22</t>
+          <t>3,26; 4,22</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 3,14</t>
+          <t>2,39; 3,16</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,02; 3,97</t>
+          <t>3,43; 4,24</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17416</t>
+          <t>18845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29974</t>
+          <t>31922</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47390</t>
+          <t>50767</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7577; 22337</t>
+          <t>6951; 22531</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2612; 12590</t>
+          <t>2052; 11749</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1918; 11172</t>
+          <t>1893; 11079</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10707; 26786</t>
+          <t>12054; 29846</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>29964; 54949</t>
+          <t>29728; 54377</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26921; 50674</t>
+          <t>26356; 49666</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23852; 47781</t>
+          <t>23258; 47939</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23541; 38406</t>
+          <t>24683; 40529</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41591; 69859</t>
+          <t>40978; 69070</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30842; 57865</t>
+          <t>32513; 58701</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28514; 53090</t>
+          <t>29072; 54604</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37925; 58821</t>
+          <t>40689; 63839</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>16815</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>44037</t>
+          <t>48289</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>59890</t>
+          <t>65104</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13836; 36118</t>
+          <t>14686; 36736</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6545; 20585</t>
+          <t>6030; 20286</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6485; 21527</t>
+          <t>5968; 19995</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7166; 26015</t>
+          <t>10874; 25964</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40568; 70534</t>
+          <t>38999; 69333</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52301; 86672</t>
+          <t>51977; 85768</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21710; 47018</t>
+          <t>22330; 46177</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34684; 54436</t>
+          <t>38319; 59761</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>60798; 96052</t>
+          <t>59922; 97660</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61610; 97796</t>
+          <t>61167; 100409</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33231; 60467</t>
+          <t>31702; 59681</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39377; 74499</t>
+          <t>52761; 79203</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16045</t>
+          <t>21359</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32086</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48131</t>
+          <t>60458</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5584; 21907</t>
+          <t>5317; 20530</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5541; 25060</t>
+          <t>5415; 24856</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6030; 21474</t>
+          <t>5829; 20941</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9895; 24949</t>
+          <t>12325; 33515</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>25649; 49470</t>
+          <t>26863; 51624</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34457; 63796</t>
+          <t>33846; 62603</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21076; 42816</t>
+          <t>21772; 43595</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15293; 45331</t>
+          <t>29885; 52209</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35147; 63580</t>
+          <t>34890; 63203</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45708; 78611</t>
+          <t>45135; 79225</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30040; 57082</t>
+          <t>30399; 55947</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30393; 62009</t>
+          <t>47611; 77827</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>20021</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>75072</t>
+          <t>80825</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94633</t>
+          <t>100846</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16537; 34691</t>
+          <t>17470; 36459</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9381; 26357</t>
+          <t>8852; 25611</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8677; 23696</t>
+          <t>8829; 24325</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12604; 30584</t>
+          <t>13153; 31169</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36343; 64475</t>
+          <t>36988; 63634</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46323; 80942</t>
+          <t>46262; 78222</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37360; 66157</t>
+          <t>36600; 66807</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>58161; 91309</t>
+          <t>66468; 97094</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>58736; 91221</t>
+          <t>58671; 90928</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>59326; 96116</t>
+          <t>61813; 97691</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49980; 84128</t>
+          <t>48985; 81389</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>76585; 113630</t>
+          <t>84882; 120968</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68876</t>
+          <t>77041</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>181169</t>
+          <t>200134</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>250045</t>
+          <t>277175</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>57390; 91669</t>
+          <t>56909; 93723</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>32689; 62370</t>
+          <t>31896; 62408</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32914; 58279</t>
+          <t>32060; 56894</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51668; 87804</t>
+          <t>60192; 93936</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>154672; 206254</t>
+          <t>152853; 207030</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>185266; 243139</t>
+          <t>184917; 244436</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>122626; 175335</t>
+          <t>123306; 171513</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>149245; 208661</t>
+          <t>178432; 226139</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>222735; 286084</t>
+          <t>224272; 290756</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>228931; 294050</t>
+          <t>227027; 293901</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166431; 217995</t>
+          <t>165567; 219283</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>215097; 282375</t>
+          <t>249208; 307629</t>
         </is>
       </c>
     </row>
